--- a/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
+++ b/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
@@ -596,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -608,6 +608,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -821,12 +824,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="14" width="8.71"/>
+    <col customWidth="1" min="1" max="5" width="8.71"/>
+    <col customWidth="1" min="6" max="6" width="19.71"/>
+    <col customWidth="1" min="7" max="7" width="8.86"/>
+    <col customWidth="1" min="8" max="8" width="8.29"/>
+    <col customWidth="1" min="9" max="9" width="11.14"/>
+    <col customWidth="1" min="10" max="14" width="8.71"/>
     <col customWidth="1" min="15" max="16" width="12.57"/>
     <col customWidth="1" min="17" max="17" width="23.14"/>
     <col customWidth="1" min="18" max="29" width="8.71"/>
-    <col customWidth="1" min="30" max="30" width="12.86"/>
-    <col customWidth="1" min="31" max="31" width="8.71"/>
+    <col customWidth="1" min="30" max="30" width="11.43"/>
+    <col customWidth="1" min="31" max="31" width="15.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8093,6 +8101,9 @@
       <c r="AB82" s="3">
         <v>13.68</v>
       </c>
+      <c r="AC82" s="5">
+        <v>3.6</v>
+      </c>
       <c r="AE82" s="3">
         <v>250.358</v>
       </c>
@@ -8267,6 +8278,9 @@
       </c>
       <c r="AB84" s="3">
         <v>1.02</v>
+      </c>
+      <c r="AC84" s="5">
+        <v>0.47</v>
       </c>
       <c r="AE84" s="3">
         <v>30.4822848</v>

--- a/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
+++ b/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
@@ -619,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -630,6 +630,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,11 +847,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="8.7109375" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="5" width="8.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" customWidth="1"/>
     <col min="8" max="8" width="8.28515625" customWidth="1"/>
@@ -3157,7 +3159,7 @@
       <c r="F26" s="4">
         <v>45617</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="7" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -3220,11 +3222,11 @@
       <c r="AB26" s="3">
         <v>20</v>
       </c>
-      <c r="AC26" s="3">
-        <v>34.11</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>18.97</v>
+      <c r="AC26" s="6">
+        <v>30</v>
+      </c>
+      <c r="AD26" s="7">
+        <v>16.690000000000001</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>72</v>
@@ -3252,7 +3254,7 @@
       <c r="F27" s="4">
         <v>45617</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -3312,11 +3314,11 @@
       <c r="AB27" s="3">
         <v>20</v>
       </c>
-      <c r="AC27" s="3">
-        <v>38.97</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>18.77</v>
+      <c r="AC27" s="7">
+        <v>34.11</v>
+      </c>
+      <c r="AD27" s="7">
+        <v>18.97</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>74</v>
@@ -3344,7 +3346,7 @@
       <c r="F28" s="4">
         <v>45617</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="7" t="s">
         <v>75</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -3407,11 +3409,11 @@
       <c r="AB28" s="3">
         <v>20</v>
       </c>
-      <c r="AC28" s="3">
-        <v>30.07</v>
-      </c>
-      <c r="AD28" s="3">
-        <v>15.23</v>
+      <c r="AC28" s="7">
+        <v>38.97</v>
+      </c>
+      <c r="AD28" s="7">
+        <v>18.77</v>
       </c>
       <c r="AF28" s="3">
         <v>1332.5820000000001</v>
@@ -3436,7 +3438,7 @@
       <c r="F29" s="4">
         <v>45617</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H29" s="3" t="s">
@@ -3499,11 +3501,11 @@
       <c r="AB29" s="3">
         <v>20</v>
       </c>
-      <c r="AC29" s="3">
-        <v>14.55</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>5.69</v>
+      <c r="AC29" s="7">
+        <v>30.07</v>
+      </c>
+      <c r="AD29" s="7">
+        <v>15.23</v>
       </c>
       <c r="AF29" s="3">
         <v>1248.499</v>
@@ -3528,7 +3530,7 @@
       <c r="F30" s="4">
         <v>45617</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="7" t="s">
         <v>78</v>
       </c>
       <c r="H30" s="3">
@@ -3591,11 +3593,11 @@
       <c r="AB30" s="3">
         <v>20</v>
       </c>
-      <c r="AC30" s="3">
-        <v>30</v>
-      </c>
-      <c r="AD30" s="3">
-        <v>16.690000000000001</v>
+      <c r="AC30" s="7">
+        <v>14.55</v>
+      </c>
+      <c r="AD30" s="7">
+        <v>5.69</v>
       </c>
       <c r="AF30" s="3">
         <v>579.08100000000002</v>
@@ -4405,7 +4407,7 @@
         <v>20</v>
       </c>
       <c r="AC39" s="3">
-        <v>25.15</v>
+        <v>35.15</v>
       </c>
       <c r="AD39" s="3">
         <v>18.2</v>
@@ -4494,7 +4496,7 @@
         <v>20</v>
       </c>
       <c r="AC40" s="3">
-        <v>25.52</v>
+        <v>35.520000000000003</v>
       </c>
       <c r="AD40" s="3">
         <v>17.36</v>
@@ -5239,7 +5241,7 @@
         <v>176.61370529999999</v>
       </c>
     </row>
-    <row r="49" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5331,7 +5333,7 @@
         <v>31.193000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5423,7 +5425,7 @@
         <v>34.548281500000002</v>
       </c>
     </row>
-    <row r="51" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5515,7 +5517,7 @@
         <v>41.29</v>
       </c>
     </row>
-    <row r="52" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5607,7 +5609,7 @@
         <v>37.481708599999997</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5699,7 +5701,7 @@
         <v>25.962922299999999</v>
       </c>
     </row>
-    <row r="54" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6818,7 +6820,7 @@
         <v>363.37691890000002</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6910,7 +6912,7 @@
         <v>30.444854299999999</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -7002,7 +7004,7 @@
         <v>37.5134951</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -7278,7 +7280,7 @@
         <v>400.27849179999998</v>
       </c>
     </row>
-    <row r="71" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7370,7 +7372,7 @@
         <v>33.473779800000003</v>
       </c>
     </row>
-    <row r="72" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>57.475637399999997</v>
       </c>
     </row>
-    <row r="73" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7646,7 +7648,7 @@
         <v>431.89406120000001</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7830,7 +7832,7 @@
         <v>404.1618411</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -8106,7 +8108,7 @@
         <v>418.39213590000003</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -8198,7 +8200,7 @@
         <v>28.873925499999999</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8379,7 +8381,7 @@
         <v>250.358</v>
       </c>
     </row>
-    <row r="83" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8471,7 +8473,7 @@
         <v>35.679000000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:32" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -9480,11 +9482,6 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AF84">
-    <filterColumn colId="11">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
+++ b/Results_isofys/05. Rasgos_Bombuscaro_Cajanuma.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$84</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="twCB5PWWkDzqpa3OwFIsLume6vcWYW6ABIUX9NFhg3M="/>
@@ -104,9 +104,6 @@
     <t>leaf 3, thickn 2</t>
   </si>
   <si>
-    <t># leaves</t>
-  </si>
-  <si>
     <t>Leaf fresh weight (g)</t>
   </si>
   <si>
@@ -116,439 +113,442 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>BoN</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>1877</t>
+  </si>
+  <si>
+    <t>Sapotaceae</t>
+  </si>
+  <si>
+    <t>Pouteria</t>
+  </si>
+  <si>
+    <t>torta</t>
+  </si>
+  <si>
+    <t>1875</t>
+  </si>
+  <si>
+    <t>NP</t>
+  </si>
+  <si>
+    <t>7543</t>
+  </si>
+  <si>
+    <t>Moraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarisia </t>
+  </si>
+  <si>
+    <t>racemosa</t>
+  </si>
+  <si>
+    <t>1860</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>8415</t>
+  </si>
+  <si>
+    <t>Hojas se colectan a 10 m de altura. el arbol se encuentra en sombra. hojas jovenes con botones florales</t>
+  </si>
+  <si>
+    <t>2068</t>
+  </si>
+  <si>
+    <t>Boton floral</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>2060</t>
+  </si>
+  <si>
+    <t>sombra y boton floral</t>
+  </si>
+  <si>
+    <t>2048</t>
+  </si>
+  <si>
+    <t>8411</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>boton floral</t>
+  </si>
+  <si>
+    <t>8402</t>
+  </si>
+  <si>
+    <t>7546</t>
+  </si>
+  <si>
+    <t>1927</t>
+  </si>
+  <si>
+    <t>1925</t>
+  </si>
+  <si>
+    <t>1942</t>
+  </si>
+  <si>
+    <t>1887</t>
+  </si>
+  <si>
+    <t>1894</t>
+  </si>
+  <si>
+    <t>1840</t>
+  </si>
+  <si>
+    <t>7540</t>
+  </si>
+  <si>
+    <t>3011</t>
+  </si>
+  <si>
+    <t>7887</t>
+  </si>
+  <si>
+    <t>8423</t>
+  </si>
+  <si>
+    <t>2074</t>
+  </si>
+  <si>
+    <t>copa quebrada</t>
+  </si>
+  <si>
+    <t>Hojas bonitas?</t>
+  </si>
+  <si>
+    <t>2120</t>
+  </si>
+  <si>
+    <t>Algunas hojas tiernas, pocas hojas en ramas</t>
+  </si>
+  <si>
+    <t>2062</t>
+  </si>
+  <si>
+    <t>Hojas en mal estado,enfermas</t>
+  </si>
+  <si>
+    <t>2119</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>8405?</t>
+  </si>
+  <si>
+    <t>7209</t>
+  </si>
+  <si>
+    <t>1930</t>
+  </si>
+  <si>
+    <t>7633</t>
+  </si>
+  <si>
+    <t>revisar 7630</t>
+  </si>
+  <si>
+    <t>7208</t>
+  </si>
+  <si>
+    <t>5786</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>inflorescencia</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2249</t>
+  </si>
+  <si>
+    <t>4997</t>
+  </si>
+  <si>
+    <t>5785</t>
+  </si>
+  <si>
+    <t>2180</t>
+  </si>
+  <si>
+    <t>2176</t>
+  </si>
+  <si>
+    <t>tronco recto hasta los 10,5 de ahi bifurcaciones al rededor de 2m que no se distinguen bien</t>
+  </si>
+  <si>
+    <t>7626</t>
+  </si>
+  <si>
+    <t>6007</t>
+  </si>
+  <si>
+    <t>8435</t>
+  </si>
+  <si>
+    <t>5791</t>
+  </si>
+  <si>
+    <t>flores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaNu </t>
+  </si>
+  <si>
+    <t>1557</t>
+  </si>
+  <si>
+    <t>Chloranthaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hedyosmun </t>
+  </si>
+  <si>
+    <t>purpurascens</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 10 en otra funda</t>
+  </si>
+  <si>
+    <t>1547</t>
+  </si>
+  <si>
+    <t>fertil</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 10 en otra funda fértil</t>
+  </si>
+  <si>
+    <t>1538</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 10 en otra funda </t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>Cunoniaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weinmania </t>
+  </si>
+  <si>
+    <t>loxensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 50 nutrientes</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>más 50</t>
+  </si>
+  <si>
+    <t>7647</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>4811</t>
+  </si>
+  <si>
+    <t>19018</t>
+  </si>
+  <si>
+    <t>a 1m de la trampa E</t>
+  </si>
+  <si>
+    <t>más 13</t>
+  </si>
+  <si>
+    <t>19017</t>
+  </si>
+  <si>
+    <t>inflorescencia. a 1m de 1500 y del 9001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 10 fértil</t>
+  </si>
+  <si>
+    <t>19016</t>
+  </si>
+  <si>
+    <t>al lado de 1441</t>
+  </si>
+  <si>
+    <t>19015</t>
+  </si>
+  <si>
+    <t>2m de la trampa E</t>
+  </si>
+  <si>
+    <t>19008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boton floral. al lado de 1166 a 1m </t>
+  </si>
+  <si>
+    <t>19007</t>
+  </si>
+  <si>
+    <t>al lado de la trampa D. inflorescencia</t>
+  </si>
+  <si>
+    <t>más 5</t>
+  </si>
+  <si>
+    <t>19006</t>
+  </si>
+  <si>
+    <t>al lado de 1028 a 2 m</t>
+  </si>
+  <si>
+    <t>19014</t>
+  </si>
+  <si>
+    <t>al lado de la trampa A</t>
+  </si>
+  <si>
+    <t>19013</t>
+  </si>
+  <si>
+    <t>inflorescencia. al lado de la trampa F</t>
+  </si>
+  <si>
+    <t>19010</t>
+  </si>
+  <si>
+    <t>inflorescencia. al lado del 1204 a 3m</t>
+  </si>
+  <si>
+    <t>19011</t>
+  </si>
+  <si>
+    <t>inflorescencia. al lado del 8931. rama principal caida y rebrote</t>
+  </si>
+  <si>
+    <t>5819</t>
+  </si>
+  <si>
+    <t>sin muchas hojas</t>
+  </si>
+  <si>
+    <t>1313</t>
+  </si>
+  <si>
+    <t>inflorescencia. pocas hojas</t>
+  </si>
+  <si>
+    <t>1318</t>
+  </si>
+  <si>
+    <t>19019</t>
+  </si>
+  <si>
+    <t>al lado de la trampa B y a 2m de la trampa E</t>
+  </si>
+  <si>
+    <t>19009</t>
+  </si>
+  <si>
+    <t>Al lado de la 1216</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>8824</t>
+  </si>
+  <si>
+    <t>sin muchas hojas e inflorescencia</t>
+  </si>
+  <si>
+    <t>19004</t>
+  </si>
+  <si>
+    <t>Trampa D</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>19003</t>
+  </si>
+  <si>
+    <t>a medio metro del 1637</t>
+  </si>
+  <si>
+    <t>1329</t>
+  </si>
+  <si>
+    <t>inflorescencia y pocas hojas</t>
+  </si>
+  <si>
+    <t>19012</t>
+  </si>
+  <si>
+    <t>inflorescencia. a 2m del arbol 4839 y a 30cm de la piola</t>
+  </si>
+  <si>
+    <t>19005</t>
+  </si>
+  <si>
+    <t>8933</t>
+  </si>
+  <si>
+    <t>5861</t>
+  </si>
+  <si>
+    <t>8941</t>
+  </si>
+  <si>
+    <t>1745</t>
+  </si>
+  <si>
+    <t>8934</t>
+  </si>
+  <si>
+    <t>compound</t>
+  </si>
+  <si>
+    <t>number of leaves</t>
+  </si>
+  <si>
     <t>Leaf area (cm²)</t>
-  </si>
-  <si>
-    <t>BoN</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>1877</t>
-  </si>
-  <si>
-    <t>Sapotaceae</t>
-  </si>
-  <si>
-    <t>Pouteria</t>
-  </si>
-  <si>
-    <t>torta</t>
-  </si>
-  <si>
-    <t>1875</t>
-  </si>
-  <si>
-    <t>NP</t>
-  </si>
-  <si>
-    <t>7543</t>
-  </si>
-  <si>
-    <t>Moraceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarisia </t>
-  </si>
-  <si>
-    <t>racemosa</t>
-  </si>
-  <si>
-    <t>1860</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>8415</t>
-  </si>
-  <si>
-    <t>Hojas se colectan a 10 m de altura. el arbol se encuentra en sombra. hojas jovenes con botones florales</t>
-  </si>
-  <si>
-    <t>2068</t>
-  </si>
-  <si>
-    <t>Boton floral</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>2060</t>
-  </si>
-  <si>
-    <t>sombra y boton floral</t>
-  </si>
-  <si>
-    <t>2048</t>
-  </si>
-  <si>
-    <t>8411</t>
-  </si>
-  <si>
-    <t>2027</t>
-  </si>
-  <si>
-    <t>boton floral</t>
-  </si>
-  <si>
-    <t>8402</t>
-  </si>
-  <si>
-    <t>7546</t>
-  </si>
-  <si>
-    <t>1927</t>
-  </si>
-  <si>
-    <t>1925</t>
-  </si>
-  <si>
-    <t>1942</t>
-  </si>
-  <si>
-    <t>1887</t>
-  </si>
-  <si>
-    <t>1894</t>
-  </si>
-  <si>
-    <t>1840</t>
-  </si>
-  <si>
-    <t>7540</t>
-  </si>
-  <si>
-    <t>3011</t>
-  </si>
-  <si>
-    <t>7887</t>
-  </si>
-  <si>
-    <t>8423</t>
-  </si>
-  <si>
-    <t>2074</t>
-  </si>
-  <si>
-    <t>copa quebrada</t>
-  </si>
-  <si>
-    <t>Hojas bonitas?</t>
-  </si>
-  <si>
-    <t>2120</t>
-  </si>
-  <si>
-    <t>Algunas hojas tiernas, pocas hojas en ramas</t>
-  </si>
-  <si>
-    <t>2062</t>
-  </si>
-  <si>
-    <t>Hojas en mal estado,enfermas</t>
-  </si>
-  <si>
-    <t>2119</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>8405?</t>
-  </si>
-  <si>
-    <t>7209</t>
-  </si>
-  <si>
-    <t>1930</t>
-  </si>
-  <si>
-    <t>7633</t>
-  </si>
-  <si>
-    <t>revisar 7630</t>
-  </si>
-  <si>
-    <t>7208</t>
-  </si>
-  <si>
-    <t>5786</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>inflorescencia</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2249</t>
-  </si>
-  <si>
-    <t>4997</t>
-  </si>
-  <si>
-    <t>5785</t>
-  </si>
-  <si>
-    <t>2180</t>
-  </si>
-  <si>
-    <t>2176</t>
-  </si>
-  <si>
-    <t>tronco recto hasta los 10,5 de ahi bifurcaciones al rededor de 2m que no se distinguen bien</t>
-  </si>
-  <si>
-    <t>7626</t>
-  </si>
-  <si>
-    <t>6007</t>
-  </si>
-  <si>
-    <t>8435</t>
-  </si>
-  <si>
-    <t>5791</t>
-  </si>
-  <si>
-    <t>flores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaNu </t>
-  </si>
-  <si>
-    <t>1557</t>
-  </si>
-  <si>
-    <t>Chloranthaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hedyosmun </t>
-  </si>
-  <si>
-    <t>purpurascens</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 10 en otra funda</t>
-  </si>
-  <si>
-    <t>1547</t>
-  </si>
-  <si>
-    <t>fertil</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 10 en otra funda fértil</t>
-  </si>
-  <si>
-    <t>1538</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 10 en otra funda </t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>Cunoniaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weinmania </t>
-  </si>
-  <si>
-    <t>loxensis</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 50 nutrientes</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>más 50</t>
-  </si>
-  <si>
-    <t>7647</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>4811</t>
-  </si>
-  <si>
-    <t>19018</t>
-  </si>
-  <si>
-    <t>a 1m de la trampa E</t>
-  </si>
-  <si>
-    <t>más 13</t>
-  </si>
-  <si>
-    <t>19017</t>
-  </si>
-  <si>
-    <t>inflorescencia. a 1m de 1500 y del 9001</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 10 fértil</t>
-  </si>
-  <si>
-    <t>19016</t>
-  </si>
-  <si>
-    <t>al lado de 1441</t>
-  </si>
-  <si>
-    <t>19015</t>
-  </si>
-  <si>
-    <t>2m de la trampa E</t>
-  </si>
-  <si>
-    <t>19008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boton floral. al lado de 1166 a 1m </t>
-  </si>
-  <si>
-    <t>19007</t>
-  </si>
-  <si>
-    <t>al lado de la trampa D. inflorescencia</t>
-  </si>
-  <si>
-    <t>más 5</t>
-  </si>
-  <si>
-    <t>19006</t>
-  </si>
-  <si>
-    <t>al lado de 1028 a 2 m</t>
-  </si>
-  <si>
-    <t>19014</t>
-  </si>
-  <si>
-    <t>al lado de la trampa A</t>
-  </si>
-  <si>
-    <t>19013</t>
-  </si>
-  <si>
-    <t>inflorescencia. al lado de la trampa F</t>
-  </si>
-  <si>
-    <t>19010</t>
-  </si>
-  <si>
-    <t>inflorescencia. al lado del 1204 a 3m</t>
-  </si>
-  <si>
-    <t>19011</t>
-  </si>
-  <si>
-    <t>inflorescencia. al lado del 8931. rama principal caida y rebrote</t>
-  </si>
-  <si>
-    <t>5819</t>
-  </si>
-  <si>
-    <t>sin muchas hojas</t>
-  </si>
-  <si>
-    <t>1313</t>
-  </si>
-  <si>
-    <t>inflorescencia. pocas hojas</t>
-  </si>
-  <si>
-    <t>1318</t>
-  </si>
-  <si>
-    <t>19019</t>
-  </si>
-  <si>
-    <t>al lado de la trampa B y a 2m de la trampa E</t>
-  </si>
-  <si>
-    <t>19009</t>
-  </si>
-  <si>
-    <t>Al lado de la 1216</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>8824</t>
-  </si>
-  <si>
-    <t>sin muchas hojas e inflorescencia</t>
-  </si>
-  <si>
-    <t>19004</t>
-  </si>
-  <si>
-    <t>Trampa D</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>19003</t>
-  </si>
-  <si>
-    <t>a medio metro del 1637</t>
-  </si>
-  <si>
-    <t>1329</t>
-  </si>
-  <si>
-    <t>inflorescencia y pocas hojas</t>
-  </si>
-  <si>
-    <t>19012</t>
-  </si>
-  <si>
-    <t>inflorescencia. a 2m del arbol 4839 y a 30cm de la piola</t>
-  </si>
-  <si>
-    <t>19005</t>
-  </si>
-  <si>
-    <t>8933</t>
-  </si>
-  <si>
-    <t>5861</t>
-  </si>
-  <si>
-    <t>8941</t>
-  </si>
-  <si>
-    <t>1745</t>
-  </si>
-  <si>
-    <t>8934</t>
-  </si>
-  <si>
-    <t>compound</t>
   </si>
 </sst>
 </file>
@@ -856,7 +856,9 @@
     <col min="7" max="7" width="8.85546875" customWidth="1"/>
     <col min="8" max="8" width="8.28515625" customWidth="1"/>
     <col min="9" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="15" width="8.7109375" customWidth="1"/>
+    <col min="10" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="15" width="8.7109375" customWidth="1"/>
     <col min="16" max="17" width="12.5703125" customWidth="1"/>
     <col min="18" max="18" width="23.140625" customWidth="1"/>
     <col min="19" max="30" width="8.7109375" customWidth="1"/>
@@ -896,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>10</v>
@@ -944,19 +946,19 @@
         <v>24</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="AF1" s="2" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
@@ -967,28 +969,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
         <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" s="4">
         <v>45611</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
@@ -1056,28 +1058,28 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3">
         <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F3" s="4">
         <v>45611</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
@@ -1145,28 +1147,28 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4">
         <v>45611</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
@@ -1234,28 +1236,28 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3">
         <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4">
         <v>45611</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
@@ -1323,28 +1325,28 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4">
         <v>45611</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -1412,28 +1414,28 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4">
         <v>45614</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -1445,7 +1447,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P7" s="3">
         <v>5.33</v>
@@ -1504,28 +1506,28 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4">
         <v>45614</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -1537,7 +1539,7 @@
         <v>10.08</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P8" s="3">
         <v>5.32</v>
@@ -1596,28 +1598,28 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9" s="4">
         <v>45614</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -1629,7 +1631,7 @@
         <v>13.4</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P9" s="3">
         <v>4.74</v>
@@ -1688,28 +1690,28 @@
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3">
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="4">
         <v>45614</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1777,28 +1779,28 @@
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="4">
         <v>45617</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
@@ -1866,28 +1868,28 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>5</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4">
         <v>45617</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
@@ -1899,7 +1901,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P12" s="3">
         <v>7.1</v>
@@ -1958,28 +1960,28 @@
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3">
         <v>6</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F13" s="4">
         <v>45615</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L13" s="3">
         <v>0</v>
@@ -1991,7 +1993,7 @@
         <v>11.1</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P13" s="3">
         <v>3.17</v>
@@ -2050,28 +2052,28 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
         <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F14" s="4">
         <v>45615</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -2083,7 +2085,7 @@
         <v>10.9</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P14" s="3">
         <v>5.54</v>
@@ -2142,28 +2144,28 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3">
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F15" s="4">
         <v>45615</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -2175,7 +2177,7 @@
         <v>10.4</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P15" s="3">
         <v>4.0199999999999996</v>
@@ -2234,28 +2236,28 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="3">
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" s="4">
         <v>45615</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L16" s="3">
         <v>0</v>
@@ -2267,7 +2269,7 @@
         <v>18</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P16" s="3">
         <v>5.44</v>
@@ -2326,28 +2328,28 @@
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3">
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17" s="4">
         <v>45615</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
@@ -2415,28 +2417,28 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F18" s="4">
         <v>45616</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
@@ -2448,7 +2450,7 @@
         <v>14.6</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P18" s="3">
         <v>5.24</v>
@@ -2507,31 +2509,31 @@
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F19" s="4">
         <v>45616</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H19" s="3">
         <v>4978</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
@@ -2543,7 +2545,7 @@
         <v>14.2</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P19" s="3">
         <v>6.94</v>
@@ -2602,31 +2604,31 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" s="3">
         <v>13</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F20" s="4">
         <v>45616</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H20" s="3">
         <v>9101</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -2694,31 +2696,31 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="3">
         <v>13</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F21" s="4">
         <v>45616</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H21" s="3">
         <v>1841</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -2786,28 +2788,28 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="3">
         <v>14</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" s="4">
         <v>45616</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2875,28 +2877,28 @@
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F23" s="4">
         <v>45616</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
@@ -2964,28 +2966,28 @@
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F24" s="4">
         <v>45616</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -3053,28 +3055,28 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D25" s="3">
         <v>2</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" s="4">
         <v>45617</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L25" s="3">
         <v>0</v>
@@ -3086,7 +3088,7 @@
         <v>14.9</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P25" s="3">
         <v>5.54</v>
@@ -3134,7 +3136,7 @@
         <v>18.05</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AF25" s="3">
         <v>1252.4929999999999</v>
@@ -3148,28 +3150,28 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" s="3">
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F26" s="4">
         <v>45617</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -3181,7 +3183,7 @@
         <v>15.5</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P26" s="3">
         <v>6.96</v>
@@ -3229,7 +3231,7 @@
         <v>16.690000000000001</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF26" s="3">
         <v>1047.2190000000001</v>
@@ -3243,28 +3245,28 @@
         <v>26</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="3">
         <v>4</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F27" s="4">
         <v>45617</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -3321,7 +3323,7 @@
         <v>18.97</v>
       </c>
       <c r="AE27" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AF27" s="3">
         <v>1362.462</v>
@@ -3335,28 +3337,28 @@
         <v>27</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="3">
         <v>3</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F28" s="4">
         <v>45617</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L28" s="3">
         <v>0</v>
@@ -3368,7 +3370,7 @@
         <v>17</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P28" s="3">
         <v>6.06</v>
@@ -3427,31 +3429,31 @@
         <v>28</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D29" s="3">
         <v>5</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F29" s="4">
         <v>45617</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -3519,31 +3521,31 @@
         <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D30" s="3">
         <v>5</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4">
         <v>45617</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H30" s="3">
         <v>2021</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>
@@ -3611,28 +3613,28 @@
         <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" s="3">
         <v>8</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F31" s="4">
         <v>45618</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L31" s="3">
         <v>0</v>
@@ -3700,28 +3702,28 @@
         <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D32" s="3">
         <v>6</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F32" s="4">
         <v>45618</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3733,7 +3735,7 @@
         <v>17.8</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P32" s="3">
         <v>5.19</v>
@@ -3792,28 +3794,28 @@
         <v>32</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3">
         <v>6</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F33" s="4">
         <v>45618</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -3881,28 +3883,28 @@
         <v>33</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D34" s="3">
         <v>9</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F34" s="4">
         <v>45618</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>
@@ -3970,28 +3972,28 @@
         <v>34</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D35" s="3">
         <v>6</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F35" s="4">
         <v>45618</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -4003,7 +4005,7 @@
         <v>13.1</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P35" s="3">
         <v>5.57</v>
@@ -4062,28 +4064,28 @@
         <v>35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D36" s="3">
         <v>6</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" s="4">
         <v>45618</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L36" s="3">
         <v>0</v>
@@ -4151,28 +4153,28 @@
         <v>36</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3">
         <v>9</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F37" s="4">
         <v>45618</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L37" s="3">
         <v>0</v>
@@ -4240,28 +4242,28 @@
         <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D38" s="3">
         <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F38" s="4">
         <v>45618</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L38" s="3">
         <v>0</v>
@@ -4329,31 +4331,31 @@
         <v>38</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D39" s="3">
         <v>11</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F39" s="4">
         <v>45619</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H39" s="3">
         <v>2203</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L39" s="3">
         <v>0</v>
@@ -4365,7 +4367,7 @@
         <v>10.119999999999999</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P39" s="3">
         <v>3.74</v>
@@ -4424,28 +4426,28 @@
         <v>39</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D40" s="3">
         <v>11</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F40" s="4">
         <v>45649</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
@@ -4513,28 +4515,28 @@
         <v>40</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F41" s="4">
         <v>45649</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -4546,7 +4548,7 @@
         <v>10.5</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P41" s="3">
         <v>5.2</v>
@@ -4605,28 +4607,28 @@
         <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F42" s="4">
         <v>45649</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -4638,7 +4640,7 @@
         <v>10.4</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P42" s="3">
         <v>5.36</v>
@@ -4697,28 +4699,28 @@
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D43" s="3">
         <v>12</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F43" s="4">
         <v>45649</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4730,7 +4732,7 @@
         <v>13.4</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P43" s="3">
         <v>3.94</v>
@@ -4789,28 +4791,28 @@
         <v>43</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3">
         <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F44" s="4">
         <v>45649</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4878,28 +4880,28 @@
         <v>44</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D45" s="3">
         <v>10</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F45" s="4">
         <v>45649</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4911,7 +4913,7 @@
         <v>15</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P45" s="3">
         <v>4.82</v>
@@ -4970,28 +4972,28 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D46" s="3">
         <v>15</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F46" s="4">
         <v>45623</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -5048,7 +5050,7 @@
         <v>3.33</v>
       </c>
       <c r="AE46" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AF46" s="3">
         <v>201.37735599999999</v>
@@ -5062,28 +5064,28 @@
         <v>2</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D47" s="3">
         <v>15</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F47" s="4">
         <v>45623</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -5095,7 +5097,7 @@
         <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P47" s="3">
         <v>6.33</v>
@@ -5143,7 +5145,7 @@
         <v>2.97</v>
       </c>
       <c r="AE47" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AF47" s="3">
         <v>187.5230679</v>
@@ -5157,28 +5159,28 @@
         <v>3</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D48" s="3">
         <v>15</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F48" s="4">
         <v>45623</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -5235,7 +5237,7 @@
         <v>2.42</v>
       </c>
       <c r="AE48" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF48" s="3">
         <v>176.61370529999999</v>
@@ -5249,28 +5251,28 @@
         <v>4</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D49" s="3">
         <v>5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F49" s="4">
         <v>45623</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L49" s="3">
         <v>1</v>
@@ -5327,7 +5329,7 @@
         <v>0.52</v>
       </c>
       <c r="AE49" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF49" s="3">
         <v>31.193000000000001</v>
@@ -5341,28 +5343,28 @@
         <v>5</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D50" s="3">
         <v>5</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F50" s="4">
         <v>45623</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L50" s="3">
         <v>1</v>
@@ -5419,7 +5421,7 @@
         <v>0.46</v>
       </c>
       <c r="AE50" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF50" s="3">
         <v>34.548281500000002</v>
@@ -5433,28 +5435,28 @@
         <v>6</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D51" s="3">
         <v>8</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F51" s="4">
         <v>45623</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L51" s="3">
         <v>1</v>
@@ -5511,7 +5513,7 @@
         <v>0.61</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AF51" s="3">
         <v>41.29</v>
@@ -5525,28 +5527,28 @@
         <v>7</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D52" s="3">
         <v>6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F52" s="4">
         <v>45623</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L52" s="3">
         <v>1</v>
@@ -5603,7 +5605,7 @@
         <v>0.47</v>
       </c>
       <c r="AE52" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AF52" s="3">
         <v>37.481708599999997</v>
@@ -5617,28 +5619,28 @@
         <v>8</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D53" s="3">
         <v>7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F53" s="4">
         <v>45623</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L53" s="3">
         <v>1</v>
@@ -5695,7 +5697,7 @@
         <v>0.31</v>
       </c>
       <c r="AE53" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AF53" s="3">
         <v>25.962922299999999</v>
@@ -5709,28 +5711,28 @@
         <v>9</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3">
         <v>6</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F54" s="4">
         <v>45623</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I54" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L54" s="3">
         <v>1</v>
@@ -5787,7 +5789,7 @@
         <v>0.46</v>
       </c>
       <c r="AE54" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AF54" s="3">
         <v>33.630206999999999</v>
@@ -5801,28 +5803,28 @@
         <v>10</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3">
         <v>14</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F55" s="4">
         <v>45628</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I55" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K55" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
@@ -5834,7 +5836,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P55" s="3">
         <v>6.87</v>
@@ -5882,7 +5884,7 @@
         <v>4.96</v>
       </c>
       <c r="AE55" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF55" s="3">
         <v>335.48921030000002</v>
@@ -5896,28 +5898,28 @@
         <v>11</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D56" s="3">
         <v>14</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F56" s="4">
         <v>45628</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I56" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -5929,7 +5931,7 @@
         <v>3</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P56" s="3">
         <v>4.66</v>
@@ -5977,7 +5979,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AE56" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AF56" s="3">
         <v>342.97277650000001</v>
@@ -5991,28 +5993,28 @@
         <v>12</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D57" s="3">
         <v>13</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F57" s="4">
         <v>45628</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I57" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -6024,7 +6026,7 @@
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P57" s="3">
         <v>4.5199999999999996</v>
@@ -6083,28 +6085,28 @@
         <v>13</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D58" s="3">
         <v>13</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F58" s="4">
         <v>45628</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -6116,7 +6118,7 @@
         <v>5</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P58" s="3">
         <v>3.92</v>
@@ -6164,7 +6166,7 @@
         <v>7.06</v>
       </c>
       <c r="AE58" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AF58" s="3">
         <v>569.72833939999998</v>
@@ -6178,28 +6180,28 @@
         <v>14</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D59" s="3">
         <v>7</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F59" s="4">
         <v>45628</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I59" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -6211,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P59" s="3">
         <v>5.92</v>
@@ -6259,7 +6261,7 @@
         <v>7.5</v>
       </c>
       <c r="AE59" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AF59" s="3">
         <v>423.10477650000001</v>
@@ -6273,28 +6275,28 @@
         <v>15</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D60" s="3">
         <v>6</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F60" s="4">
         <v>45628</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I60" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -6306,7 +6308,7 @@
         <v>3.5</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P60" s="3">
         <v>5.0999999999999996</v>
@@ -6354,7 +6356,7 @@
         <v>7.58</v>
       </c>
       <c r="AE60" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AF60" s="3">
         <v>528.09348180000006</v>
@@ -6368,28 +6370,28 @@
         <v>16</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D61" s="3">
         <v>5</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F61" s="4">
         <v>45628</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I61" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -6401,7 +6403,7 @@
         <v>4</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P61" s="3">
         <v>5.21</v>
@@ -6460,28 +6462,28 @@
         <v>17</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D62" s="3">
         <v>12</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F62" s="4">
         <v>45629</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I62" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -6493,7 +6495,7 @@
         <v>6</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P62" s="3">
         <v>4.38</v>
@@ -6552,28 +6554,28 @@
         <v>18</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D63" s="3">
         <v>12</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F63" s="4">
         <v>45629</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
@@ -6585,7 +6587,7 @@
         <v>4</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P63" s="3">
         <v>4.12</v>
@@ -6644,28 +6646,28 @@
         <v>19</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D64" s="3">
         <v>9</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F64" s="4">
         <v>45629</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I64" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
@@ -6677,7 +6679,7 @@
         <v>4</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P64" s="3">
         <v>4.51</v>
@@ -6736,28 +6738,28 @@
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D65" s="3">
         <v>10</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F65" s="4">
         <v>45629</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L65" s="3">
         <v>0</v>
@@ -6769,7 +6771,7 @@
         <v>3</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P65" s="3">
         <v>5.42</v>
@@ -6828,28 +6830,28 @@
         <v>21</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D66" s="3">
         <v>10</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F66" s="4">
         <v>45629</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L66" s="3">
         <v>1</v>
@@ -6861,7 +6863,7 @@
         <v>6</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P66" s="3">
         <v>5</v>
@@ -6920,28 +6922,28 @@
         <v>22</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D67" s="3">
         <v>12</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F67" s="4">
         <v>45629</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L67" s="3">
         <v>1</v>
@@ -6953,7 +6955,7 @@
         <v>6</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P67" s="3">
         <v>4.97</v>
@@ -7012,28 +7014,28 @@
         <v>23</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D68" s="3">
         <v>12</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F68" s="4">
         <v>45629</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I68" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L68" s="3">
         <v>1</v>
@@ -7045,7 +7047,7 @@
         <v>7</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P68" s="3">
         <v>4.68</v>
@@ -7104,28 +7106,28 @@
         <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D69" s="3">
         <v>16</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F69" s="4">
         <v>45629</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I69" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L69" s="3">
         <v>0</v>
@@ -7137,7 +7139,7 @@
         <v>5</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P69" s="3">
         <v>4.8</v>
@@ -7196,28 +7198,28 @@
         <v>25</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D70" s="3">
         <v>9</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F70" s="4">
         <v>45629</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -7229,7 +7231,7 @@
         <v>4</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P70" s="3">
         <v>5.27</v>
@@ -7288,28 +7290,28 @@
         <v>26</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D71" s="3">
         <v>9</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F71" s="4">
         <v>45629</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I71" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L71" s="3">
         <v>1</v>
@@ -7321,7 +7323,7 @@
         <v>7</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P71" s="3">
         <v>5.18</v>
@@ -7380,28 +7382,28 @@
         <v>27</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D72" s="3">
         <v>9</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F72" s="4">
         <v>45629</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I72" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L72" s="3">
         <v>1</v>
@@ -7413,7 +7415,7 @@
         <v>6</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P72" s="3">
         <v>5.64</v>
@@ -7472,28 +7474,28 @@
         <v>28</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F73" s="4">
         <v>45629</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I73" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L73" s="3">
         <v>1</v>
@@ -7505,7 +7507,7 @@
         <v>3</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P73" s="3">
         <v>6.17</v>
@@ -7564,28 +7566,28 @@
         <v>29</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F74" s="4">
         <v>45630</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I74" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K74" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L74" s="3">
         <v>0</v>
@@ -7597,7 +7599,7 @@
         <v>3.7</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P74" s="3">
         <v>4.53</v>
@@ -7656,28 +7658,28 @@
         <v>30</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F75" s="4">
         <v>45630</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I75" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L75" s="3">
         <v>1</v>
@@ -7689,7 +7691,7 @@
         <v>4.5</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P75" s="3">
         <v>5.33</v>
@@ -7748,28 +7750,28 @@
         <v>31</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F76" s="4">
         <v>45630</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L76" s="3">
         <v>0</v>
@@ -7781,7 +7783,7 @@
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P76" s="3">
         <v>4.1399999999999997</v>
@@ -7840,28 +7842,28 @@
         <v>32</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D77" s="3">
         <v>11</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F77" s="4">
         <v>45630</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I77" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L77" s="3">
         <v>1</v>
@@ -7873,7 +7875,7 @@
         <v>6</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P77" s="3">
         <v>4.95</v>
@@ -7932,28 +7934,28 @@
         <v>33</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D78" s="3">
         <v>11</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F78" s="4">
         <v>45630</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I78" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L78" s="3">
         <v>0</v>
@@ -7965,7 +7967,7 @@
         <v>4.5</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P78" s="3">
         <v>5.19</v>
@@ -8024,28 +8026,28 @@
         <v>34</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D79" s="3">
         <v>3</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F79" s="4">
         <v>45630</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I79" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L79" s="3">
         <v>0</v>
@@ -8057,7 +8059,7 @@
         <v>3</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P79" s="3">
         <v>3.38</v>
@@ -8116,28 +8118,28 @@
         <v>35</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F80" s="4">
         <v>45630</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I80" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L80" s="3">
         <v>1</v>
@@ -8149,7 +8151,7 @@
         <v>5.5</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P80" s="3">
         <v>5.34</v>
@@ -8208,28 +8210,28 @@
         <v>36</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D81" s="3">
         <v>1</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F81" s="4">
         <v>45630</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I81" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K81" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L81" s="3">
         <v>1</v>
@@ -8241,7 +8243,7 @@
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P81" s="3">
         <v>5.0599999999999996</v>
@@ -8300,28 +8302,28 @@
         <v>37</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D82" s="3">
         <v>4</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F82" s="4">
         <v>45630</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I82" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="L82" s="3">
         <v>0</v>
@@ -8389,28 +8391,28 @@
         <v>38</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D83" s="3">
         <v>3</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F83" s="4">
         <v>45630</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I83" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L83" s="3">
         <v>1</v>
@@ -8422,7 +8424,7 @@
         <v>7</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P83" s="3">
         <v>5.88</v>
@@ -8481,28 +8483,28 @@
         <v>39</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F84" s="4">
         <v>45630</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I84" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="L84" s="3">
         <v>1</v>
@@ -8514,7 +8516,7 @@
         <v>6.5</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P84" s="3">
         <v>4.76</v>
